--- a/task269/golden/coaching_wards_2027.xlsx
+++ b/task269/golden/coaching_wards_2027.xlsx
@@ -151,7 +151,7 @@
     <t>Coaching nurse 2027: wards whose staff performed hand hygiene at fewer than 80 per cent of the moments on their AM and PM shifts in 2025-26 (terms 2.1 to 2.4).</t>
   </si>
   <si>
-    <t>Hospital-onset BSI: episodes under the hospital's surveillance definitions (version 3), attributed to the ward the patient was on when the culture was collected.</t>
+    <t>Hospital-onset BSI: episodes under the hospital's surveillance protocol (version 3), attributed to the ward the patient was on when the culture was collected.</t>
   </si>
   <si>
     <t>Hand rub put out: bottles issued to the ward's cost centre less returns, and the dispenser refills fitted on the ward, each refill counted once.</t>
